--- a/deployment/artifacts/report_dashboard_template.xlsx
+++ b/deployment/artifacts/report_dashboard_template.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8AADDE6-D617-4F52-A45A-ED702BA01718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
